--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios155.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios155.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.91934962736313</v>
+        <v>27.12445164247194</v>
       </c>
     </row>
     <row r="3">
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.17737008394547</v>
+        <v>33.12476542513664</v>
       </c>
     </row>
     <row r="4">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.11664521650256</v>
+        <v>25.66029609589989</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.87382356726933</v>
+        <v>24.73889828712912</v>
       </c>
     </row>
     <row r="6">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.8122600211392</v>
+        <v>32.73144265246271</v>
       </c>
     </row>
     <row r="7">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.17416186039875</v>
+        <v>21.52675764849945</v>
       </c>
     </row>
     <row r="8">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31.51325843950432</v>
+        <v>27.23542442929922</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>31.66201156463809</v>
+        <v>33.51941514667246</v>
       </c>
     </row>
     <row r="10">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>26.25918755468106</v>
+        <v>26.04119582780901</v>
       </c>
     </row>
     <row r="11">
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.72470897536926</v>
+        <v>24.87688167365211</v>
       </c>
     </row>
     <row r="12">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27.99389230440484</v>
+        <v>32.58497134145912</v>
       </c>
     </row>
     <row r="13">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.72699642824747</v>
+        <v>21.56536888754603</v>
       </c>
     </row>
     <row r="14">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.81266486098011</v>
+        <v>27.24528641936691</v>
       </c>
     </row>
     <row r="15">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>31.14586616175179</v>
+        <v>33.7056274889384</v>
       </c>
     </row>
     <row r="16">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>26.54094044292867</v>
+        <v>25.26760610870734</v>
       </c>
     </row>
     <row r="17">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28.40594875938191</v>
+        <v>25.24420071282895</v>
       </c>
     </row>
     <row r="18">
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28.08270019422512</v>
+        <v>32.49589686047381</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24.52104221111842</v>
+        <v>21.17520446177121</v>
       </c>
     </row>
     <row r="20">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.98483950066611</v>
+        <v>27.28006027081649</v>
       </c>
     </row>
     <row r="21">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>31.40106645951946</v>
+        <v>32.52677676539652</v>
       </c>
     </row>
     <row r="22">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.98138658454563</v>
+        <v>25.89036176615701</v>
       </c>
     </row>
     <row r="23">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28.77650799434992</v>
+        <v>25.12782470659361</v>
       </c>
     </row>
     <row r="24">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.14162308607812</v>
+        <v>32.94747197654592</v>
       </c>
     </row>
     <row r="25">
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.70220485945359</v>
+        <v>21.12863585765485</v>
       </c>
     </row>
     <row r="26">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31.80679678120577</v>
+        <v>27.0346954821531</v>
       </c>
     </row>
     <row r="27">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.63329607421563</v>
+        <v>33.01986392290021</v>
       </c>
     </row>
     <row r="28">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.03467044000562</v>
+        <v>26.18488351398837</v>
       </c>
     </row>
     <row r="29">
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>28.87065050409986</v>
+        <v>25.12072344766357</v>
       </c>
     </row>
     <row r="30">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>28.3484030095661</v>
+        <v>32.29563412837216</v>
       </c>
     </row>
     <row r="31">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>24.94519118865276</v>
+        <v>21.3477211455508</v>
       </c>
     </row>
     <row r="32">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>30.92072431917631</v>
+        <v>29.63444491783731</v>
       </c>
     </row>
     <row r="33">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>31.3770303415164</v>
+        <v>22.73099396032523</v>
       </c>
     </row>
     <row r="34">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>25.62744415445265</v>
+        <v>20.67390643275809</v>
       </c>
     </row>
     <row r="35">
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.8977180215093</v>
+        <v>28.45765994808262</v>
       </c>
     </row>
     <row r="36">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>29.89536605571962</v>
+        <v>32.08908053104163</v>
       </c>
     </row>
     <row r="37">
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>28.18212058284488</v>
+        <v>26.2780412085214</v>
       </c>
     </row>
     <row r="38">
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>30.81709354483559</v>
+        <v>29.69337291948554</v>
       </c>
     </row>
     <row r="39">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31.85681762158222</v>
+        <v>22.57169482725498</v>
       </c>
     </row>
     <row r="40">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>25.14073045098201</v>
+        <v>20.82113903477397</v>
       </c>
     </row>
     <row r="41">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26.34706157938048</v>
+        <v>28.48423399192464</v>
       </c>
     </row>
     <row r="42">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>30.05101473854911</v>
+        <v>31.75943239763188</v>
       </c>
     </row>
     <row r="43">
@@ -1119,7 +1119,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>28.35913029046805</v>
+        <v>26.55615718734973</v>
       </c>
     </row>
     <row r="44">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>30.83910084208694</v>
+        <v>29.50424137872755</v>
       </c>
     </row>
     <row r="45">
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>31.44740668032113</v>
+        <v>22.3323075840303</v>
       </c>
     </row>
     <row r="46">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>25.39934080284122</v>
+        <v>20.7864946041157</v>
       </c>
     </row>
     <row r="47">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>27.13785164649234</v>
+        <v>28.66657287497036</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>29.52128732668382</v>
+        <v>32.82304206790047</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>28.10987127227283</v>
+        <v>26.7148932948662</v>
       </c>
     </row>
     <row r="50">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>30.75394859612418</v>
+        <v>29.68195403293793</v>
       </c>
     </row>
     <row r="51">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>30.85539369271132</v>
+        <v>22.49616370095731</v>
       </c>
     </row>
     <row r="52">
@@ -1263,7 +1263,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>25.41139374712041</v>
+        <v>20.42058481452671</v>
       </c>
     </row>
     <row r="53">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>27.1837383759104</v>
+        <v>28.54364142778768</v>
       </c>
     </row>
     <row r="54">
@@ -1295,7 +1295,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>30.00785015387478</v>
+        <v>32.23480314288297</v>
       </c>
     </row>
     <row r="55">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>28.41009781502899</v>
+        <v>27.32524198699894</v>
       </c>
     </row>
     <row r="56">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>30.39778533235208</v>
+        <v>29.54875460685063</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>31.17751844843094</v>
+        <v>22.58081077609426</v>
       </c>
     </row>
     <row r="58">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>25.3606489357374</v>
+        <v>20.81284739301471</v>
       </c>
     </row>
     <row r="59">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>26.65451472524785</v>
+        <v>28.21753972262115</v>
       </c>
     </row>
     <row r="60">
@@ -1391,7 +1391,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30.3860973147267</v>
+        <v>32.58356467800201</v>
       </c>
     </row>
     <row r="61">
@@ -1407,7 +1407,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>28.50278221416357</v>
+        <v>26.86886432652332</v>
       </c>
     </row>
     <row r="62">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>24.53703695949854</v>
+        <v>28.89136628262288</v>
       </c>
     </row>
     <row r="63">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>21.62386612101809</v>
+        <v>26.90994812286158</v>
       </c>
     </row>
     <row r="64">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>23.97174665375313</v>
+        <v>20.51760233117985</v>
       </c>
     </row>
     <row r="65">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>24.86227670346223</v>
+        <v>25.6201731212333</v>
       </c>
     </row>
     <row r="66">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>28.9256475253227</v>
+        <v>28.7860309413482</v>
       </c>
     </row>
     <row r="67">
@@ -1503,7 +1503,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>25.16558269352524</v>
+        <v>30.78260273874037</v>
       </c>
     </row>
     <row r="68">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>24.61162441012175</v>
+        <v>28.38068650770089</v>
       </c>
     </row>
     <row r="69">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>21.29942506786799</v>
+        <v>27.00312068955846</v>
       </c>
     </row>
     <row r="70">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>23.7970857492971</v>
+        <v>20.25392745983839</v>
       </c>
     </row>
     <row r="71">
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>24.69664544733208</v>
+        <v>25.85361090628541</v>
       </c>
     </row>
     <row r="72">
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>28.75672863134269</v>
+        <v>28.17431352871256</v>
       </c>
     </row>
     <row r="73">
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>25.40434722905785</v>
+        <v>30.1434297540413</v>
       </c>
     </row>
     <row r="74">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>24.73345783968834</v>
+        <v>28.36011465848967</v>
       </c>
     </row>
     <row r="75">
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>21.60342858232932</v>
+        <v>27.28552272085795</v>
       </c>
     </row>
     <row r="76">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>23.65370043329462</v>
+        <v>20.04773010566911</v>
       </c>
     </row>
     <row r="77">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25.09565572481884</v>
+        <v>26.3871779333641</v>
       </c>
     </row>
     <row r="78">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>28.01778861468474</v>
+        <v>28.39393160443773</v>
       </c>
     </row>
     <row r="79">
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25.47062456728049</v>
+        <v>30.02576281094766</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>25.31493482280714</v>
+        <v>28.89781159991372</v>
       </c>
     </row>
     <row r="81">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21.57216010483277</v>
+        <v>26.82264494199301</v>
       </c>
     </row>
     <row r="82">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.80757645405523</v>
+        <v>20.27978794446976</v>
       </c>
     </row>
     <row r="83">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>24.49413795499133</v>
+        <v>26.32408989173987</v>
       </c>
     </row>
     <row r="84">
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>28.42421183047409</v>
+        <v>28.15805278979747</v>
       </c>
     </row>
     <row r="85">
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>25.77268504060201</v>
+        <v>30.17839352713929</v>
       </c>
     </row>
     <row r="86">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>24.26399569565274</v>
+        <v>28.73911439644161</v>
       </c>
     </row>
     <row r="87">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>21.90146561235987</v>
+        <v>27.36922858327996</v>
       </c>
     </row>
     <row r="88">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>23.5132511218421</v>
+        <v>19.98348254699305</v>
       </c>
     </row>
     <row r="89">
@@ -1855,7 +1855,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>24.51645671798219</v>
+        <v>25.64132301010144</v>
       </c>
     </row>
     <row r="90">
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>28.35334957130556</v>
+        <v>28.76745336116675</v>
       </c>
     </row>
     <row r="91">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>25.57328851974819</v>
+        <v>30.21223671215233</v>
       </c>
     </row>
     <row r="92">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.24312962406443</v>
+        <v>30.07163211016761</v>
       </c>
     </row>
     <row r="93">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>32.21511358521954</v>
+        <v>23.14339060470079</v>
       </c>
     </row>
     <row r="94">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>27.82642095428601</v>
+        <v>27.07852603369812</v>
       </c>
     </row>
     <row r="95">
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>28.44817071821442</v>
+        <v>26.98429642010593</v>
       </c>
     </row>
     <row r="96">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>31.92707437839602</v>
+        <v>28.05120412492593</v>
       </c>
     </row>
     <row r="97">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>21.41583707629864</v>
+        <v>28.18276503664457</v>
       </c>
     </row>
     <row r="98">
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>27.80348895536896</v>
+        <v>30.55615996112148</v>
       </c>
     </row>
     <row r="99">
@@ -2015,7 +2015,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>32.07304919689601</v>
+        <v>23.17276996177764</v>
       </c>
     </row>
     <row r="100">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>27.09934348852297</v>
+        <v>26.93913135908804</v>
       </c>
     </row>
     <row r="101">
@@ -2047,7 +2047,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>28.98203705382054</v>
+        <v>27.0985254647486</v>
       </c>
     </row>
     <row r="102">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>32.44160621359374</v>
+        <v>27.69662300199008</v>
       </c>
     </row>
     <row r="103">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>21.51739474965873</v>
+        <v>28.60895572203984</v>
       </c>
     </row>
     <row r="104">
@@ -2095,7 +2095,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>27.88484877193358</v>
+        <v>30.34403108196433</v>
       </c>
     </row>
     <row r="105">
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>31.65219643274769</v>
+        <v>22.87420960054327</v>
       </c>
     </row>
     <row r="106">
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.01344321140315</v>
+        <v>27.52658164988267</v>
       </c>
     </row>
     <row r="107">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>28.97757645198385</v>
+        <v>27.03289754499814</v>
       </c>
     </row>
     <row r="108">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>32.33955906855734</v>
+        <v>28.19915792884421</v>
       </c>
     </row>
     <row r="109">
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>21.63521592524911</v>
+        <v>28.92395241037025</v>
       </c>
     </row>
     <row r="110">
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>27.59890768355528</v>
+        <v>29.92288521061137</v>
       </c>
     </row>
     <row r="111">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>32.06668187213933</v>
+        <v>22.88964971844497</v>
       </c>
     </row>
     <row r="112">
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>26.9332645680699</v>
+        <v>27.02141091161677</v>
       </c>
     </row>
     <row r="113">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>29.01567845624555</v>
+        <v>26.7021390494218</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2255,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>32.14779116887134</v>
+        <v>27.9476692415588</v>
       </c>
     </row>
     <row r="115">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>21.46108671640549</v>
+        <v>28.48237534831329</v>
       </c>
     </row>
     <row r="116">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>27.55544572079673</v>
+        <v>30.07949057611119</v>
       </c>
     </row>
     <row r="117">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>32.15216802672804</v>
+        <v>23.2542648707654</v>
       </c>
     </row>
     <row r="118">
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>27.15519231097185</v>
+        <v>27.2674723070124</v>
       </c>
     </row>
     <row r="119">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>28.82225468247428</v>
+        <v>27.31308671035972</v>
       </c>
     </row>
     <row r="120">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>32.53573182581185</v>
+        <v>27.89521151009924</v>
       </c>
     </row>
     <row r="121">
@@ -2367,7 +2367,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>21.50529567937019</v>
+        <v>29.1576721660454</v>
       </c>
     </row>
     <row r="122">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>31.89870723063236</v>
+        <v>32.19004896545693</v>
       </c>
     </row>
     <row r="123">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27.60792198732423</v>
+        <v>30.34522911157405</v>
       </c>
     </row>
     <row r="124">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>28.82782400523421</v>
+        <v>22.48366936818038</v>
       </c>
     </row>
     <row r="125">
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>24.95349587933073</v>
+        <v>27.2651204035143</v>
       </c>
     </row>
     <row r="126">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>25.17418086197657</v>
+        <v>30.92453070714119</v>
       </c>
     </row>
     <row r="127">
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>29.57545526990961</v>
+        <v>30.01743117264935</v>
       </c>
     </row>
     <row r="128">
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>32.46788771507571</v>
+        <v>32.14128685154849</v>
       </c>
     </row>
     <row r="129">
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>27.62101513786004</v>
+        <v>30.58529316266471</v>
       </c>
     </row>
     <row r="130">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>28.08076634439792</v>
+        <v>22.53460041367748</v>
       </c>
     </row>
     <row r="131">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>25.25066607723842</v>
+        <v>26.72316359096767</v>
       </c>
     </row>
     <row r="132">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>25.16524724202132</v>
+        <v>30.85539838633474</v>
       </c>
     </row>
     <row r="133">
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>29.42055145761601</v>
+        <v>30.05987245345765</v>
       </c>
     </row>
     <row r="134">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>31.38272649149899</v>
+        <v>32.05838698692707</v>
       </c>
     </row>
     <row r="135">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>28.03589369641053</v>
+        <v>30.22629378625565</v>
       </c>
     </row>
     <row r="136">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>28.26829908082128</v>
+        <v>22.76641057791419</v>
       </c>
     </row>
     <row r="137">
@@ -2623,7 +2623,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>25.1814820062395</v>
+        <v>27.23875815667228</v>
       </c>
     </row>
     <row r="138">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>25.34234031517467</v>
+        <v>30.71984937393472</v>
       </c>
     </row>
     <row r="139">
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>28.91131694701971</v>
+        <v>29.85044318866588</v>
       </c>
     </row>
     <row r="140">
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>31.88311792208058</v>
+        <v>32.00851952525436</v>
       </c>
     </row>
     <row r="141">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>27.97857320965822</v>
+        <v>30.2577487357097</v>
       </c>
     </row>
     <row r="142">
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>28.64517597200389</v>
+        <v>22.80836617764898</v>
       </c>
     </row>
     <row r="143">
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>25.1448959781742</v>
+        <v>27.28636977255902</v>
       </c>
     </row>
     <row r="144">
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>25.83952852079543</v>
+        <v>31.32946892529927</v>
       </c>
     </row>
     <row r="145">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>28.73317114281478</v>
+        <v>30.11870775612203</v>
       </c>
     </row>
     <row r="146">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>32.53114930509269</v>
+        <v>31.54918358117559</v>
       </c>
     </row>
     <row r="147">
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>27.81685827951895</v>
+        <v>30.32053874353241</v>
       </c>
     </row>
     <row r="148">
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>28.35768848062075</v>
+        <v>22.84410399067452</v>
       </c>
     </row>
     <row r="149">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>24.66623730817553</v>
+        <v>27.27361708258432</v>
       </c>
     </row>
     <row r="150">
@@ -2831,7 +2831,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>25.29080300866876</v>
+        <v>31.15342309401957</v>
       </c>
     </row>
     <row r="151">
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>29.45879721109754</v>
+        <v>30.95291820718838</v>
       </c>
     </row>
   </sheetData>
